--- a/Inputs/PFNA_template_parameters_Model.xlsx
+++ b/Inputs/PFNA_template_parameters_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/bernstein_amanda_epa_gov/Documents/Documents/PKWG_models/pbpk_template_project/Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/schlosser_paul_epa_gov/Documents/mcsim-5.6.5/PBPK_Model_Template_Mod/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{14D51B71-0158-4B22-B7A5-EFF2D66679BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96E32CA1-C622-4674-BE06-C8A8872AAB84}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{14D51B71-0158-4B22-B7A5-EFF2D66679BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFC3250C-84F2-4AEA-9A80-99C8E02C7CE1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
+    <workbookView xWindow="-27525" yWindow="1545" windowWidth="25740" windowHeight="12795" xr2:uid="{089E7848-11EB-427A-89EA-83825F220BA0}"/>
   </bookViews>
   <sheets>
     <sheet name="MKimRecreateBW" sheetId="9" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="240">
   <si>
     <t>Code</t>
   </si>
@@ -751,6 +751,9 @@
   </si>
   <si>
     <t>num.blood.comp</t>
+  </si>
+  <si>
+    <t>"2580" listed, sum of blood flows except lung &amp; filtrate:</t>
   </si>
 </sst>
 </file>
@@ -942,10 +945,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -983,7 +990,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1089,7 +1096,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1231,7 +1238,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1240,18 +1247,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADCAA70-43B6-4F02-AE2A-67A6EACE5958}">
   <dimension ref="A1:G104"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1278,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1285,7 +1292,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1296,7 +1303,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1307,7 +1314,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1324,7 +1331,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1341,7 +1348,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1355,7 +1362,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1369,7 +1376,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>238</v>
       </c>
@@ -1386,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>136</v>
       </c>
@@ -1403,7 +1410,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>137</v>
       </c>
@@ -1420,7 +1427,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -1437,7 +1444,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -1454,7 +1461,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>166</v>
       </c>
@@ -1471,7 +1478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -1483,13 +1490,13 @@
       </c>
       <c r="E15">
         <f>1-SUM(E76:E85)</f>
-        <v>-0.99224806201550408</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -1504,7 +1511,7 @@
         <v>0.70472000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1524,7 +1531,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
@@ -1544,7 +1551,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1561,7 +1568,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1575,7 +1582,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>230</v>
       </c>
@@ -1593,7 +1600,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -1607,7 +1614,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1622,13 +1629,17 @@
       </c>
       <c r="E24">
         <f>F24/(G20^E20)</f>
-        <v>7297.3419818451703</v>
+        <v>14538.115421195416</v>
       </c>
       <c r="F24">
-        <v>2580</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <f>2580+2560</f>
+        <v>5140</v>
+      </c>
+      <c r="G24" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
@@ -1641,8 +1652,12 @@
       <c r="E25">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G25">
+        <f>234+18+24+450+520+450+828+36</f>
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>142</v>
       </c>
@@ -1663,7 +1678,7 @@
         <v>81030</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>143</v>
       </c>
@@ -1683,7 +1698,7 @@
         <v>24850</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -1697,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>144</v>
       </c>
@@ -1718,7 +1733,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>145</v>
       </c>
@@ -1742,7 +1757,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>146</v>
       </c>
@@ -1756,7 +1771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
@@ -1776,7 +1791,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
@@ -1790,7 +1805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -1804,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -1818,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>167</v>
       </c>
@@ -1832,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -1853,7 +1868,7 @@
         <v>0.371</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>226</v>
       </c>
@@ -1867,7 +1882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>227</v>
       </c>
@@ -1881,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>228</v>
       </c>
@@ -1895,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>147</v>
       </c>
@@ -1909,7 +1924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>148</v>
       </c>
@@ -1923,7 +1938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>149</v>
       </c>
@@ -1937,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>150</v>
       </c>
@@ -1951,7 +1966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>151</v>
       </c>
@@ -1965,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>152</v>
       </c>
@@ -1979,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>153</v>
       </c>
@@ -1993,7 +2008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>154</v>
       </c>
@@ -2007,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
@@ -2018,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>170</v>
       </c>
@@ -2029,7 +2044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -2040,7 +2055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>184</v>
       </c>
@@ -2055,13 +2070,13 @@
       </c>
       <c r="E52">
         <f>F52/F24</f>
-        <v>0.10077519379844961</v>
+        <v>5.0583657587548639E-2</v>
       </c>
       <c r="F52">
         <v>260</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>162</v>
       </c>
@@ -2075,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>163</v>
       </c>
@@ -2086,7 +2101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>198</v>
       </c>
@@ -2100,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>200</v>
       </c>
@@ -2114,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>233</v>
       </c>
@@ -2131,7 +2146,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>42</v>
       </c>
@@ -2145,7 +2160,7 @@
         <v>2.7200000000000002E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
@@ -2162,7 +2177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>81</v>
       </c>
@@ -2183,7 +2198,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>138</v>
       </c>
@@ -2197,7 +2212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>140</v>
       </c>
@@ -2211,7 +2226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>84</v>
       </c>
@@ -2225,7 +2240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>91</v>
       </c>
@@ -2246,7 +2261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>92</v>
       </c>
@@ -2267,7 +2282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>93</v>
       </c>
@@ -2288,7 +2303,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>94</v>
       </c>
@@ -2309,7 +2324,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>95</v>
       </c>
@@ -2330,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>96</v>
       </c>
@@ -2351,7 +2366,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>97</v>
       </c>
@@ -2365,7 +2380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>98</v>
       </c>
@@ -2379,7 +2394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>99</v>
       </c>
@@ -2393,7 +2408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>100</v>
       </c>
@@ -2407,7 +2422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>155</v>
       </c>
@@ -2428,7 +2443,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>106</v>
       </c>
@@ -2443,13 +2458,13 @@
       </c>
       <c r="E76">
         <f>F76/F24</f>
-        <v>0.1744186046511628</v>
+        <v>8.7548638132295714E-2</v>
       </c>
       <c r="F76">
         <v>450</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>107</v>
       </c>
@@ -2464,13 +2479,13 @@
       </c>
       <c r="E77">
         <f>F77/F24</f>
-        <v>0.32093023255813952</v>
+        <v>0.16108949416342414</v>
       </c>
       <c r="F77">
         <v>828</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>108</v>
       </c>
@@ -2485,13 +2500,13 @@
       </c>
       <c r="E78">
         <f>F78/F24</f>
-        <v>0.20155038759689922</v>
+        <v>0.10116731517509728</v>
       </c>
       <c r="F78">
         <v>520</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>109</v>
       </c>
@@ -2506,13 +2521,13 @@
       </c>
       <c r="E79" s="4">
         <f>F79/F24</f>
-        <v>1</v>
+        <v>0.50194552529182879</v>
       </c>
       <c r="F79">
         <v>2580</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>110</v>
       </c>
@@ -2527,13 +2542,13 @@
       </c>
       <c r="E80">
         <f>F80/F24</f>
-        <v>9.0697674418604657E-2</v>
+        <v>4.5525291828793772E-2</v>
       </c>
       <c r="F80">
         <v>234</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -2547,7 +2562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>112</v>
       </c>
@@ -2561,7 +2576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>113</v>
       </c>
@@ -2575,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>114</v>
       </c>
@@ -2589,7 +2604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>157</v>
       </c>
@@ -2604,13 +2619,13 @@
       </c>
       <c r="E85">
         <f>F85/F24</f>
-        <v>0.20465116279069767</v>
+        <v>0.10272373540856031</v>
       </c>
       <c r="F85">
         <v>528</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>123</v>
       </c>
@@ -2621,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>124</v>
       </c>
@@ -2635,7 +2650,7 @@
         <v>6.6E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>125</v>
       </c>
@@ -2649,7 +2664,7 @@
         <v>1.1860999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>126</v>
       </c>
@@ -2663,7 +2678,7 @@
         <v>0.12770000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>127</v>
       </c>
@@ -2677,7 +2692,7 @@
         <v>2.92E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>128</v>
       </c>
@@ -2691,7 +2706,7 @@
         <v>1.8599999999999998E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>129</v>
       </c>
@@ -2702,7 +2717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>130</v>
       </c>
@@ -2713,7 +2728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>131</v>
       </c>
@@ -2724,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>132</v>
       </c>
@@ -2735,7 +2750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>159</v>
       </c>
@@ -2749,7 +2764,7 @@
         <v>7.3000000000000001E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>0</v>
       </c>
@@ -2766,7 +2781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -2774,7 +2789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>0</v>
       </c>
@@ -2789,7 +2804,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>75</v>
       </c>
@@ -2797,7 +2812,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,7 +2820,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,18 +2860,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A6F7D2-4BD1-490A-99D2-964D9A503D54}">
   <dimension ref="A1:G104"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2876,7 +2891,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2890,7 +2905,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2901,7 +2916,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -2912,7 +2927,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -2929,7 +2944,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2946,7 +2961,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -2960,7 +2975,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -2974,7 +2989,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>238</v>
       </c>
@@ -2991,7 +3006,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>136</v>
       </c>
@@ -3008,7 +3023,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>137</v>
       </c>
@@ -3025,7 +3040,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
@@ -3042,7 +3057,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -3059,7 +3074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>166</v>
       </c>
@@ -3076,7 +3091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>192</v>
       </c>
@@ -3088,13 +3103,13 @@
       </c>
       <c r="E15">
         <f>1-SUM(E76:E85)</f>
-        <v>-0.99224806201550408</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>195</v>
       </c>
@@ -3109,7 +3124,7 @@
         <v>0.70472000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -3129,7 +3144,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
@@ -3149,7 +3164,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -3166,7 +3181,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -3180,7 +3195,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>230</v>
       </c>
@@ -3198,7 +3213,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -3212,7 +3227,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
@@ -3227,13 +3242,17 @@
       </c>
       <c r="E24">
         <f>F24/(G20^E20)</f>
-        <v>7297.3419818451703</v>
+        <v>14538.115421195416</v>
       </c>
       <c r="F24">
-        <v>2580</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <f>2580+2560</f>
+        <v>5140</v>
+      </c>
+      <c r="G24" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
@@ -3246,8 +3265,12 @@
       <c r="E25">
         <v>0.47</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G25">
+        <f>234+18+24+450+520+450+828+36</f>
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>142</v>
       </c>
@@ -3268,7 +3291,7 @@
         <v>34530</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>143</v>
       </c>
@@ -3288,7 +3311,7 @@
         <v>24850</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -3302,7 +3325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>144</v>
       </c>
@@ -3323,7 +3346,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>145</v>
       </c>
@@ -3347,7 +3370,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>146</v>
       </c>
@@ -3361,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
@@ -3381,7 +3404,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
@@ -3395,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -3409,7 +3432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -3423,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>167</v>
       </c>
@@ -3437,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -3458,7 +3481,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>226</v>
       </c>
@@ -3472,7 +3495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>227</v>
       </c>
@@ -3486,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>228</v>
       </c>
@@ -3500,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>147</v>
       </c>
@@ -3514,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>148</v>
       </c>
@@ -3528,7 +3551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>149</v>
       </c>
@@ -3542,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>150</v>
       </c>
@@ -3556,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>151</v>
       </c>
@@ -3570,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>152</v>
       </c>
@@ -3584,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>153</v>
       </c>
@@ -3598,7 +3621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>154</v>
       </c>
@@ -3612,7 +3635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
@@ -3623,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>170</v>
       </c>
@@ -3634,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
@@ -3645,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>184</v>
       </c>
@@ -3660,13 +3683,13 @@
       </c>
       <c r="E52">
         <f>F52/F24</f>
-        <v>0.10077519379844961</v>
+        <v>5.0583657587548639E-2</v>
       </c>
       <c r="F52">
         <v>260</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>162</v>
       </c>
@@ -3680,7 +3703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>163</v>
       </c>
@@ -3691,7 +3714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>198</v>
       </c>
@@ -3705,7 +3728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>200</v>
       </c>
@@ -3719,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>233</v>
       </c>
@@ -3736,7 +3759,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>42</v>
       </c>
@@ -3750,7 +3773,7 @@
         <v>3.32E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
@@ -3767,7 +3790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>81</v>
       </c>
@@ -3788,7 +3811,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>138</v>
       </c>
@@ -3802,7 +3825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>140</v>
       </c>
@@ -3816,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>84</v>
       </c>
@@ -3830,7 +3853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>91</v>
       </c>
@@ -3851,7 +3874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>92</v>
       </c>
@@ -3872,7 +3895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>93</v>
       </c>
@@ -3893,7 +3916,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>94</v>
       </c>
@@ -3914,7 +3937,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>95</v>
       </c>
@@ -3935,7 +3958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>96</v>
       </c>
@@ -3949,14 +3972,14 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <f>F70/(G20*1000)</f>
+        <f>F70/(G$20*1000)</f>
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="F70">
         <v>0.8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>97</v>
       </c>
@@ -3970,7 +3993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>98</v>
       </c>
@@ -3984,7 +4007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>99</v>
       </c>
@@ -3998,7 +4021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>100</v>
       </c>
@@ -4012,7 +4035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>155</v>
       </c>
@@ -4033,7 +4056,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>106</v>
       </c>
@@ -4048,13 +4071,13 @@
       </c>
       <c r="E76">
         <f>F76/F24</f>
-        <v>0.1744186046511628</v>
+        <v>8.7548638132295714E-2</v>
       </c>
       <c r="F76">
         <v>450</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>107</v>
       </c>
@@ -4069,13 +4092,13 @@
       </c>
       <c r="E77">
         <f>F77/F24</f>
-        <v>0.32093023255813952</v>
+        <v>0.16108949416342414</v>
       </c>
       <c r="F77">
         <v>828</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>108</v>
       </c>
@@ -4090,13 +4113,13 @@
       </c>
       <c r="E78">
         <f>F78/F24</f>
-        <v>0.20155038759689922</v>
+        <v>0.10116731517509728</v>
       </c>
       <c r="F78">
         <v>520</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>109</v>
       </c>
@@ -4111,13 +4134,13 @@
       </c>
       <c r="E79" s="4">
         <f>F79/F24</f>
-        <v>1</v>
+        <v>0.50194552529182879</v>
       </c>
       <c r="F79">
         <v>2580</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>110</v>
       </c>
@@ -4132,13 +4155,13 @@
       </c>
       <c r="E80">
         <f>F80/F24</f>
-        <v>9.0697674418604657E-2</v>
+        <v>4.5525291828793772E-2</v>
       </c>
       <c r="F80">
         <v>234</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>111</v>
       </c>
@@ -4152,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>112</v>
       </c>
@@ -4166,7 +4189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>113</v>
       </c>
@@ -4180,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>114</v>
       </c>
@@ -4194,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>157</v>
       </c>
@@ -4209,13 +4232,13 @@
       </c>
       <c r="E85">
         <f>F85/F24</f>
-        <v>0.20465116279069767</v>
+        <v>0.10272373540856031</v>
       </c>
       <c r="F85">
         <v>528</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>123</v>
       </c>
@@ -4226,7 +4249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>124</v>
       </c>
@@ -4240,7 +4263,7 @@
         <v>6.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>125</v>
       </c>
@@ -4254,7 +4277,7 @@
         <v>0.46650000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>126</v>
       </c>
@@ -4268,7 +4291,7 @@
         <v>0.24709999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>127</v>
       </c>
@@ -4282,7 +4305,7 @@
         <v>5.62E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>128</v>
       </c>
@@ -4296,7 +4319,7 @@
         <v>3.39E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>129</v>
       </c>
@@ -4307,7 +4330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>130</v>
       </c>
@@ -4318,7 +4341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>131</v>
       </c>
@@ -4329,7 +4352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>132</v>
       </c>
@@ -4340,7 +4363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>159</v>
       </c>
@@ -4354,7 +4377,7 @@
         <v>1.2699999999999999E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>0</v>
       </c>
@@ -4371,7 +4394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -4379,7 +4402,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>0</v>
       </c>
@@ -4394,7 +4417,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>75</v>
       </c>
@@ -4402,7 +4425,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>77</v>
       </c>
@@ -4410,7 +4433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>79</v>
       </c>
@@ -4995,7 +5018,26 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FF55FA5-82CC-42D6-90BE-E93B4AFF9514}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FF55FA5-82CC-42D6-90BE-E93B4AFF9514}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
+    <ds:schemaRef ds:uri="41d9f072-86bf-4c63-b117-debf50ff4701"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5008,6 +5050,7 @@
     <ds:schemaRef ds:uri="4ffa91fb-a0ff-4ac5-b2db-65c790d184a4"/>
     <ds:schemaRef ds:uri="93237db7-bebb-43bb-9414-bc3313990c09"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint.v3"/>
+    <ds:schemaRef ds:uri="2ba80736-48fa-4d73-aaff-bacaeeed013a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>